--- a/doc/install-package/补助模板.xlsx
+++ b/doc/install-package/补助模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\poor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\RuoYi-Vue\doc\install-package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBF2250-6DFA-47EB-8374-E20DC5E86BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19377749-754B-44BC-98E4-AF0F64BE6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="3330" windowWidth="26340" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="2670" windowWidth="26715" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>身份证号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,86 +45,11 @@
     <t>金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>372422197102241217</t>
-  </si>
-  <si>
-    <t>372422195503251230</t>
-  </si>
-  <si>
-    <t>371426198610251277</t>
-  </si>
-  <si>
-    <t>372422195004161214</t>
-  </si>
-  <si>
-    <t>372422195403211215</t>
-  </si>
-  <si>
-    <t>372422195610051234</t>
-  </si>
-  <si>
-    <t>372422195701221219</t>
-  </si>
-  <si>
-    <t>372422195201091219</t>
-  </si>
-  <si>
-    <t>372422195609091212</t>
-  </si>
-  <si>
-    <t>372422197301291217</t>
-  </si>
-  <si>
-    <t>372422195105071218</t>
-  </si>
-  <si>
-    <t>372422194604011215</t>
-  </si>
-  <si>
-    <t>372422195508291215</t>
-  </si>
-  <si>
-    <t>372422197005271211</t>
-  </si>
-  <si>
-    <t>372422195308031232</t>
-  </si>
-  <si>
-    <t>372422196510161211</t>
-  </si>
-  <si>
-    <t>372422196912281216</t>
-  </si>
-  <si>
-    <t>372422195602141213</t>
-  </si>
-  <si>
-    <t>372422195604101231</t>
-  </si>
-  <si>
-    <t>372422196009031229</t>
-  </si>
-  <si>
-    <t>372422195708291252</t>
-  </si>
-  <si>
-    <t>372422197810191257</t>
-  </si>
-  <si>
-    <t>372422197210027242</t>
-  </si>
-  <si>
-    <t>372422197504121218</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_);\(0.00\)"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,12 +99,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -460,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.125" style="1" customWidth="1"/>
@@ -474,198 +398,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4">
-        <v>2898</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="4">
-        <v>2898</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
